--- a/AAII_Financials/Yearly/BLNE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BLNE_YR_FIN.xlsx
@@ -1774,10 +1774,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>12100</v>
+        <v>400</v>
       </c>
       <c r="E48" s="3">
-        <v>16000</v>
+        <v>1500</v>
       </c>
       <c r="F48" s="3">
         <v>800</v>
@@ -1804,10 +1804,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>38100</v>
+        <v>49800</v>
       </c>
       <c r="E49" s="3">
-        <v>38200</v>
+        <v>52800</v>
       </c>
       <c r="F49" s="3">
         <v>4200</v>
